--- a/Assets/Resources/DataFiles/EnemyData/ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/ExcelFile/EnemyData.xlsx
@@ -891,6 +891,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C3:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." type="list">
+      <formula1>=ComboBox!$A$2:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." type="list">
+      <formula1>=ComboBox!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -902,81 +910,66 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
-  <cols>
-    <col width="12.5" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="11" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>EnemyGrade</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>AttackType</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Melee</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Ranged</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Hidden</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n"/>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/Resources/DataFiles/EnemyData/ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/ExcelFile/EnemyData.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="41.3984375" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -573,6 +573,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -635,6 +640,11 @@
           <t>patternId</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>expReward</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -681,6 +691,9 @@
       <c r="L3" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="M3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -727,6 +740,9 @@
       <c r="L4" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="M4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -773,6 +789,9 @@
       <c r="L5" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="M5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -818,6 +837,9 @@
       </c>
       <c r="L6" s="1" t="n">
         <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -913,57 +935,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>EnemyGrade</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>AttackType</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Melee</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Ranged</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>Hidden</t>
         </is>
